--- a/Documents/廣韻/廣韻三十八聲母.xlsx
+++ b/Documents/廣韻/廣韻三十八聲母.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\Piau-Im\Documents\廣韻\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlanJui\work\Piau-Im\Documents\廣韻\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59A7E67D-531E-4948-821B-0D475966D417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D623E397-7600-45B3-BB20-0CA06512C654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="67080" yWindow="-120" windowWidth="16440" windowHeight="28320" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="廣韻三十八聲母" sheetId="1" r:id="rId1"/>
+    <sheet name="廣韻41聲【閩南語聲韻學】" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="259">
   <si>
     <t>今名</t>
   </si>
@@ -408,13 +409,542 @@
   </si>
   <si>
     <t>[∅]</t>
+  </si>
+  <si>
+    <t>發音部位
+舊名</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>發音部位
+新名</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>發音方法</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>全清</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>次清</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>全濁</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>次濁（清濁）</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>重唇</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雙唇</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>p</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>幫</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ph</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>滂</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>並</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>m</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>明</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄅ</t>
+  </si>
+  <si>
+    <t>邊</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄆ</t>
+  </si>
+  <si>
+    <t>頗</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄇ</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>毛</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>輕唇</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>唇齒</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>f</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>非</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>敷</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>奉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>b</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>微</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏ</t>
+  </si>
+  <si>
+    <t>喜</t>
+  </si>
+  <si>
+    <t>ㆠ</t>
+  </si>
+  <si>
+    <t>門</t>
+  </si>
+  <si>
+    <t>舌音</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>舌頭</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>舌尖中</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>t</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>端</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>th</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>透</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>定</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>n</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>泥</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄉ</t>
+  </si>
+  <si>
+    <t>地</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄊ</t>
+  </si>
+  <si>
+    <t>他</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄋ</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>舌上</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>舌尖後</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>知</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>徹</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>澄</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>娘</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>地</t>
+  </si>
+  <si>
+    <t>他</t>
+  </si>
+  <si>
+    <t>ㄋ</t>
+  </si>
+  <si>
+    <t>耐</t>
+  </si>
+  <si>
+    <t>齒音</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>齒頭</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>舌尖前</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ts</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>精</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>tsh</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>清</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>從</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄗ</t>
+  </si>
+  <si>
+    <t>曾</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄘ</t>
+  </si>
+  <si>
+    <t>出</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆡ</t>
+  </si>
+  <si>
+    <t>入</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>心</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>邪</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙ</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>時</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄙ</t>
+  </si>
+  <si>
+    <t>時</t>
+  </si>
+  <si>
+    <t>正齒近齒頭</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>莊</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>初</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>牀</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>曾</t>
+  </si>
+  <si>
+    <t>疏</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄒ</t>
+  </si>
+  <si>
+    <t>正齒近舌上</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>舌面前</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>照</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>神</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄐ</t>
+  </si>
+  <si>
+    <t>ㄑ</t>
+  </si>
+  <si>
+    <t>審</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>禪</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>牙音</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>舌根</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>k</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>見</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>kh</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>溪</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>g</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>群</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ng</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>疑</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄍ</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>求</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄎ</t>
+  </si>
+  <si>
+    <t>去</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㆣ</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>語</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄫ</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>雅</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ʔ</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>影</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ø</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>英</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>h</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>曉</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>匣</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ʔ</t>
+  </si>
+  <si>
+    <t>為</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄏ</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>喜</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ø</t>
+  </si>
+  <si>
+    <t>英</t>
+  </si>
+  <si>
+    <t>半元音</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>喻</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>半舌音</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>l</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>來</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>ㄌ</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>柳</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>半齒音</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>j</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>日</t>
+    <phoneticPr fontId="18" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="28">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -514,8 +1044,118 @@
       <family val="1"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Noto Serif TC Black"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Noto Serif TC Black"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Noto Serif TC Black"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF0C0301"/>
+      <name val="Noto Serif TC Black"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFF0000"/>
+      <name val="Noto Serif TC Black"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="Charis SIL"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="8" tint="-0.249977111117893"/>
+      <name val="Noto Sans TC Black"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color theme="7" tint="-0.249977111117893"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="霞鶩文楷 TC"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -558,8 +1198,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -718,14 +1364,114 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="dashed">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="dashed">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </right>
+      <top style="dashed">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="dashed">
+        <color theme="0" tint="-0.14996795556505021"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -760,7 +1506,22 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -784,26 +1545,35 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -811,10 +1581,10 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -823,66 +1593,190 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="distributed" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="distributed" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="17" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="distributed" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="distributed" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="distributed" textRotation="255" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="distributed" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="distributed" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="distributed" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="distributed" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="distributed" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="distributed" indent="2"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="一般 2" xfId="2" xr:uid="{E10D8577-4A44-482E-92C1-F9396F774627}"/>
     <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -896,6 +1790,55 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>626619</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>3714</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="圖片 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AEF1F8DD-11A5-47EA-9B29-C6AE6C2066A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="685800" y="22726650"/>
+          <a:ext cx="5341494" cy="2918364"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1208,31 +2151,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="11" customFormat="1" ht="25.5">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="23" t="s">
+      <c r="B1" s="48"/>
+      <c r="C1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
       <c r="I1" s="10"/>
     </row>
     <row r="2" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="B2" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="26"/>
+      <c r="D2" s="52"/>
       <c r="E2" s="8" t="s">
         <v>5</v>
       </c>
@@ -1248,10 +2191,10 @@
       <c r="I2" s="12"/>
     </row>
     <row r="3" spans="1:9" s="13" customFormat="1" ht="25.5">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
+      <c r="A3" s="51"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
       <c r="E3" s="9" t="s">
         <v>9</v>
       </c>
@@ -1267,16 +2210,16 @@
       <c r="I3" s="12"/>
     </row>
     <row r="4" spans="1:9" ht="30">
-      <c r="A4" s="14" t="s">
+      <c r="A4" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="19"/>
+      <c r="D4" s="24"/>
       <c r="E4" s="3" t="s">
         <v>16</v>
       </c>
@@ -1291,10 +2234,10 @@
       </c>
     </row>
     <row r="5" spans="1:9" ht="30">
-      <c r="A5" s="15"/>
-      <c r="B5" s="17"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="21"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="26"/>
       <c r="E5" s="4" t="s">
         <v>20</v>
       </c>
@@ -1309,16 +2252,16 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="30">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="23" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="19"/>
+      <c r="D6" s="24"/>
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
@@ -1327,10 +2270,10 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:9" ht="30">
-      <c r="A7" s="28"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="21"/>
+      <c r="A7" s="19"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="26"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4" t="s">
@@ -1339,14 +2282,14 @@
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="30">
-      <c r="A8" s="28"/>
-      <c r="B8" s="16" t="s">
+      <c r="A8" s="19"/>
+      <c r="B8" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="39" t="s">
         <v>30</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -1363,10 +2306,10 @@
       </c>
     </row>
     <row r="9" spans="1:9" ht="30">
-      <c r="A9" s="15"/>
-      <c r="B9" s="17"/>
-      <c r="C9" s="30"/>
-      <c r="D9" s="33"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="41"/>
       <c r="E9" s="4" t="s">
         <v>35</v>
       </c>
@@ -1381,14 +2324,14 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="30">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="32" t="s">
+      <c r="C10" s="38"/>
+      <c r="D10" s="39" t="s">
         <v>40</v>
       </c>
       <c r="E10" s="3" t="s">
@@ -1405,10 +2348,10 @@
       </c>
     </row>
     <row r="11" spans="1:9" ht="30">
-      <c r="A11" s="35"/>
-      <c r="B11" s="17"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="33"/>
+      <c r="A11" s="44"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="47"/>
+      <c r="D11" s="41"/>
       <c r="E11" s="4" t="s">
         <v>45</v>
       </c>
@@ -1423,16 +2366,16 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="30">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="37" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="32" t="s">
+      <c r="D12" s="39" t="s">
         <v>51</v>
       </c>
       <c r="E12" s="3" t="s">
@@ -1447,10 +2390,10 @@
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="1:9" ht="30">
-      <c r="A13" s="28"/>
-      <c r="B13" s="17"/>
-      <c r="C13" s="30"/>
-      <c r="D13" s="37"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="40"/>
       <c r="E13" s="4" t="s">
         <v>55</v>
       </c>
@@ -1463,12 +2406,12 @@
       <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="30">
-      <c r="A14" s="28"/>
-      <c r="B14" s="16" t="s">
+      <c r="A14" s="19"/>
+      <c r="B14" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="30"/>
-      <c r="D14" s="37"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="40"/>
       <c r="E14" s="3" t="s">
         <v>59</v>
       </c>
@@ -1479,10 +2422,10 @@
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="1:9" ht="30">
-      <c r="A15" s="15"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="33"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="41"/>
       <c r="E15" s="4" t="s">
         <v>61</v>
       </c>
@@ -1493,14 +2436,14 @@
       <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="30">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="42" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="39" t="s">
+      <c r="C16" s="38"/>
+      <c r="D16" s="45" t="s">
         <v>64</v>
       </c>
       <c r="E16" s="3" t="s">
@@ -1515,10 +2458,10 @@
       <c r="H16" s="3"/>
     </row>
     <row r="17" spans="1:9" ht="30">
-      <c r="A17" s="38"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="40"/>
+      <c r="A17" s="43"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="46"/>
       <c r="E17" s="4" t="s">
         <v>68</v>
       </c>
@@ -1531,12 +2474,12 @@
       <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="30">
-      <c r="A18" s="38"/>
-      <c r="B18" s="16" t="s">
+      <c r="A18" s="43"/>
+      <c r="B18" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="40"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="46"/>
       <c r="E18" s="3" t="s">
         <v>71</v>
       </c>
@@ -1545,13 +2488,13 @@
       <c r="H18" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="I18" s="41"/>
+      <c r="I18" s="31"/>
     </row>
     <row r="19" spans="1:9" ht="30">
-      <c r="A19" s="35"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="40"/>
+      <c r="A19" s="44"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="46"/>
       <c r="E19" s="4" t="s">
         <v>73</v>
       </c>
@@ -1560,17 +2503,17 @@
       <c r="H19" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="I19" s="41"/>
+      <c r="I19" s="31"/>
     </row>
     <row r="20" spans="1:9" ht="30">
-      <c r="A20" s="14" t="s">
+      <c r="A20" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="32" t="s">
         <v>49</v>
       </c>
-      <c r="C20" s="36"/>
-      <c r="D20" s="44" t="s">
+      <c r="C20" s="27"/>
+      <c r="D20" s="34" t="s">
         <v>76</v>
       </c>
       <c r="E20" s="5" t="s">
@@ -1585,10 +2528,10 @@
       <c r="H20" s="3"/>
     </row>
     <row r="21" spans="1:9" ht="30">
-      <c r="A21" s="28"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="36"/>
-      <c r="D21" s="45"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="27"/>
+      <c r="D21" s="35"/>
       <c r="E21" s="6" t="s">
         <v>80</v>
       </c>
@@ -1601,12 +2544,12 @@
       <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:9" ht="30">
-      <c r="A22" s="28"/>
-      <c r="B22" s="42" t="s">
+      <c r="A22" s="19"/>
+      <c r="B22" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="45"/>
+      <c r="C22" s="27"/>
+      <c r="D22" s="35"/>
       <c r="E22" s="5" t="s">
         <v>83</v>
       </c>
@@ -1617,10 +2560,10 @@
       <c r="H22" s="3"/>
     </row>
     <row r="23" spans="1:9" ht="30">
-      <c r="A23" s="28"/>
-      <c r="B23" s="43"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="46"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="33"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="36"/>
       <c r="E23" s="6" t="s">
         <v>85</v>
       </c>
@@ -1631,14 +2574,14 @@
       <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:9" ht="30">
-      <c r="A24" s="28"/>
-      <c r="B24" s="47" t="s">
+      <c r="A24" s="19"/>
+      <c r="B24" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="49"/>
+      <c r="D24" s="28"/>
       <c r="E24" s="7"/>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -1647,10 +2590,10 @@
       </c>
     </row>
     <row r="25" spans="1:9" ht="30">
-      <c r="A25" s="15"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="21"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="30"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="26"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
@@ -1659,16 +2602,16 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="30">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="23" t="s">
         <v>92</v>
       </c>
-      <c r="D26" s="19"/>
+      <c r="D26" s="24"/>
       <c r="E26" s="3" t="s">
         <v>93</v>
       </c>
@@ -1683,10 +2626,10 @@
       </c>
     </row>
     <row r="27" spans="1:9" ht="30">
-      <c r="A27" s="28"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="21"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="26"/>
       <c r="E27" s="4" t="s">
         <v>97</v>
       </c>
@@ -1701,14 +2644,14 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="30">
-      <c r="A28" s="28"/>
-      <c r="B28" s="16" t="s">
+      <c r="A28" s="19"/>
+      <c r="B28" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="D28" s="19"/>
+      <c r="D28" s="24"/>
       <c r="E28" s="3" t="s">
         <v>103</v>
       </c>
@@ -1721,10 +2664,10 @@
       </c>
     </row>
     <row r="29" spans="1:9" ht="30">
-      <c r="A29" s="15"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="36"/>
-      <c r="D29" s="49"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="28"/>
       <c r="E29" s="4" t="s">
         <v>106</v>
       </c>
@@ -1737,14 +2680,14 @@
       </c>
     </row>
     <row r="30" spans="1:9" ht="30">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="B30" s="47" t="s">
+      <c r="B30" s="29" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="36"/>
-      <c r="D30" s="49"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="28"/>
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
@@ -1753,10 +2696,10 @@
       </c>
     </row>
     <row r="31" spans="1:9" ht="30">
-      <c r="A31" s="15"/>
-      <c r="B31" s="48"/>
-      <c r="C31" s="36"/>
-      <c r="D31" s="49"/>
+      <c r="A31" s="20"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="27"/>
+      <c r="D31" s="28"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -1765,14 +2708,14 @@
       </c>
     </row>
     <row r="32" spans="1:9" ht="30">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="C32" s="36"/>
-      <c r="D32" s="49"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="28"/>
       <c r="E32" s="3" t="s">
         <v>114</v>
       </c>
@@ -1781,10 +2724,10 @@
       <c r="H32" s="3"/>
     </row>
     <row r="33" spans="1:8" ht="30">
-      <c r="A33" s="28"/>
-      <c r="B33" s="48"/>
-      <c r="C33" s="36"/>
-      <c r="D33" s="49"/>
+      <c r="A33" s="19"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="27"/>
+      <c r="D33" s="28"/>
       <c r="E33" s="4" t="s">
         <v>115</v>
       </c>
@@ -1793,12 +2736,12 @@
       <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" ht="30">
-      <c r="A34" s="28"/>
-      <c r="B34" s="47" t="s">
+      <c r="A34" s="19"/>
+      <c r="B34" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="36"/>
-      <c r="D34" s="49"/>
+      <c r="C34" s="27"/>
+      <c r="D34" s="28"/>
       <c r="E34" s="3" t="s">
         <v>103</v>
       </c>
@@ -1811,10 +2754,10 @@
       </c>
     </row>
     <row r="35" spans="1:8" ht="30">
-      <c r="A35" s="15"/>
-      <c r="B35" s="48"/>
-      <c r="C35" s="36"/>
-      <c r="D35" s="49"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="27"/>
+      <c r="D35" s="28"/>
       <c r="E35" s="4" t="s">
         <v>117</v>
       </c>
@@ -1827,12 +2770,12 @@
       </c>
     </row>
     <row r="36" spans="1:8" ht="30">
-      <c r="A36" s="50" t="s">
+      <c r="A36" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="B36" s="51"/>
-      <c r="C36" s="36"/>
-      <c r="D36" s="49"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="27"/>
+      <c r="D36" s="28"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
@@ -1841,10 +2784,10 @@
       </c>
     </row>
     <row r="37" spans="1:8" ht="30">
-      <c r="A37" s="52"/>
-      <c r="B37" s="53"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="21"/>
+      <c r="A37" s="16"/>
+      <c r="B37" s="17"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="26"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="4"/>
@@ -1854,6 +2797,39 @@
     </row>
   </sheetData>
   <mergeCells count="44">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C4:D5"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:D7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C23"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="D16:D19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="I18:I19"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C24:D25"/>
     <mergeCell ref="A36:B37"/>
     <mergeCell ref="A26:A29"/>
     <mergeCell ref="B26:B27"/>
@@ -1865,39 +2841,6 @@
     <mergeCell ref="A32:A35"/>
     <mergeCell ref="B32:B33"/>
     <mergeCell ref="B34:B35"/>
-    <mergeCell ref="I18:I19"/>
-    <mergeCell ref="A20:A25"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="D20:D23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C24:D25"/>
-    <mergeCell ref="A12:A15"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C23"/>
-    <mergeCell ref="D12:D15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="D16:D19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:D7"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:D5"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:D3"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <hyperlinks>
@@ -1986,4 +2929,1218 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F05A4CF-B8EE-4B4F-8E5D-83D7FA8A1CE7}">
+  <dimension ref="B1:O58"/>
+  <sheetFormatPr defaultRowHeight="38.25" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="9" style="95"/>
+    <col min="2" max="2" width="7" style="54" customWidth="1"/>
+    <col min="3" max="3" width="11.875" style="54" customWidth="1" outlineLevel="1"/>
+    <col min="4" max="4" width="18.5" style="54" customWidth="1" outlineLevel="1"/>
+    <col min="5" max="12" width="12.25" style="55" customWidth="1"/>
+    <col min="13" max="13" width="14.375" style="56" customWidth="1"/>
+    <col min="14" max="15" width="9" style="57"/>
+    <col min="16" max="16384" width="9" style="95"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:13" ht="10.5" customHeight="1"/>
+    <row r="2" spans="2:13">
+      <c r="B2" s="58" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="60" t="s">
+        <v>122</v>
+      </c>
+      <c r="E2" s="61" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2" s="62"/>
+      <c r="G2" s="62"/>
+      <c r="H2" s="62"/>
+      <c r="I2" s="62"/>
+      <c r="J2" s="62"/>
+      <c r="K2" s="62"/>
+      <c r="L2" s="63"/>
+    </row>
+    <row r="3" spans="2:13" ht="32.25" customHeight="1">
+      <c r="B3" s="64"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="66"/>
+      <c r="E3" s="67" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3" s="68"/>
+      <c r="G3" s="67" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="68"/>
+      <c r="I3" s="67" t="s">
+        <v>126</v>
+      </c>
+      <c r="J3" s="68"/>
+      <c r="K3" s="67" t="s">
+        <v>127</v>
+      </c>
+      <c r="L3" s="68"/>
+    </row>
+    <row r="4" spans="2:13" ht="51">
+      <c r="B4" s="69" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="70" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="71" t="s">
+        <v>129</v>
+      </c>
+      <c r="E4" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="F4" s="73" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="H4" s="73" t="s">
+        <v>133</v>
+      </c>
+      <c r="I4" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="J4" s="73" t="s">
+        <v>134</v>
+      </c>
+      <c r="K4" s="72" t="s">
+        <v>135</v>
+      </c>
+      <c r="L4" s="73" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="2:13" ht="50.25">
+      <c r="B5" s="74"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="76"/>
+      <c r="E5" s="77" t="s">
+        <v>137</v>
+      </c>
+      <c r="F5" s="78" t="s">
+        <v>138</v>
+      </c>
+      <c r="G5" s="77" t="s">
+        <v>139</v>
+      </c>
+      <c r="H5" s="78" t="s">
+        <v>140</v>
+      </c>
+      <c r="I5" s="77" t="s">
+        <v>137</v>
+      </c>
+      <c r="J5" s="78" t="s">
+        <v>138</v>
+      </c>
+      <c r="K5" s="77" t="s">
+        <v>141</v>
+      </c>
+      <c r="L5" s="78" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" ht="51">
+      <c r="B6" s="74"/>
+      <c r="C6" s="70" t="s">
+        <v>143</v>
+      </c>
+      <c r="D6" s="71" t="s">
+        <v>144</v>
+      </c>
+      <c r="E6" s="79" t="s">
+        <v>145</v>
+      </c>
+      <c r="F6" s="80" t="s">
+        <v>146</v>
+      </c>
+      <c r="G6" s="79" t="s">
+        <v>145</v>
+      </c>
+      <c r="H6" s="80" t="s">
+        <v>147</v>
+      </c>
+      <c r="I6" s="79" t="s">
+        <v>145</v>
+      </c>
+      <c r="J6" s="80" t="s">
+        <v>148</v>
+      </c>
+      <c r="K6" s="81" t="s">
+        <v>149</v>
+      </c>
+      <c r="L6" s="80" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" ht="50.25">
+      <c r="B7" s="82"/>
+      <c r="C7" s="75"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="83" t="s">
+        <v>151</v>
+      </c>
+      <c r="F7" s="84" t="s">
+        <v>152</v>
+      </c>
+      <c r="G7" s="83" t="s">
+        <v>151</v>
+      </c>
+      <c r="H7" s="84" t="s">
+        <v>152</v>
+      </c>
+      <c r="I7" s="83" t="s">
+        <v>151</v>
+      </c>
+      <c r="J7" s="84" t="s">
+        <v>152</v>
+      </c>
+      <c r="K7" s="83" t="s">
+        <v>153</v>
+      </c>
+      <c r="L7" s="84" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="2:13" ht="51">
+      <c r="B8" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="70" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="71" t="s">
+        <v>157</v>
+      </c>
+      <c r="E8" s="72" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" s="73" t="s">
+        <v>159</v>
+      </c>
+      <c r="G8" s="72" t="s">
+        <v>160</v>
+      </c>
+      <c r="H8" s="73" t="s">
+        <v>161</v>
+      </c>
+      <c r="I8" s="72" t="s">
+        <v>158</v>
+      </c>
+      <c r="J8" s="73" t="s">
+        <v>162</v>
+      </c>
+      <c r="K8" s="72" t="s">
+        <v>163</v>
+      </c>
+      <c r="L8" s="73" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" ht="50.25">
+      <c r="B9" s="74"/>
+      <c r="C9" s="75"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="77" t="s">
+        <v>165</v>
+      </c>
+      <c r="F9" s="78" t="s">
+        <v>166</v>
+      </c>
+      <c r="G9" s="77" t="s">
+        <v>167</v>
+      </c>
+      <c r="H9" s="78" t="s">
+        <v>168</v>
+      </c>
+      <c r="I9" s="77" t="s">
+        <v>165</v>
+      </c>
+      <c r="J9" s="78" t="s">
+        <v>166</v>
+      </c>
+      <c r="K9" s="77" t="s">
+        <v>169</v>
+      </c>
+      <c r="L9" s="78" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="2:13" ht="51">
+      <c r="B10" s="74"/>
+      <c r="C10" s="70" t="s">
+        <v>171</v>
+      </c>
+      <c r="D10" s="71" t="s">
+        <v>172</v>
+      </c>
+      <c r="E10" s="79" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" s="80" t="s">
+        <v>173</v>
+      </c>
+      <c r="G10" s="79" t="s">
+        <v>160</v>
+      </c>
+      <c r="H10" s="80" t="s">
+        <v>174</v>
+      </c>
+      <c r="I10" s="79" t="s">
+        <v>158</v>
+      </c>
+      <c r="J10" s="80" t="s">
+        <v>175</v>
+      </c>
+      <c r="K10" s="81" t="s">
+        <v>163</v>
+      </c>
+      <c r="L10" s="80" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="11" spans="2:13" ht="50.25">
+      <c r="B11" s="82"/>
+      <c r="C11" s="75"/>
+      <c r="D11" s="76"/>
+      <c r="E11" s="83" t="s">
+        <v>165</v>
+      </c>
+      <c r="F11" s="84" t="s">
+        <v>177</v>
+      </c>
+      <c r="G11" s="83" t="s">
+        <v>167</v>
+      </c>
+      <c r="H11" s="84" t="s">
+        <v>178</v>
+      </c>
+      <c r="I11" s="83" t="s">
+        <v>165</v>
+      </c>
+      <c r="J11" s="84" t="s">
+        <v>177</v>
+      </c>
+      <c r="K11" s="83" t="s">
+        <v>179</v>
+      </c>
+      <c r="L11" s="84" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="12" spans="2:13" ht="51">
+      <c r="B12" s="85" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" s="86" t="s">
+        <v>182</v>
+      </c>
+      <c r="D12" s="71" t="s">
+        <v>183</v>
+      </c>
+      <c r="E12" s="72" t="s">
+        <v>184</v>
+      </c>
+      <c r="F12" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="G12" s="72" t="s">
+        <v>186</v>
+      </c>
+      <c r="H12" s="73" t="s">
+        <v>187</v>
+      </c>
+      <c r="I12" s="72" t="s">
+        <v>184</v>
+      </c>
+      <c r="J12" s="73" t="s">
+        <v>188</v>
+      </c>
+      <c r="K12" s="72"/>
+      <c r="L12" s="73"/>
+    </row>
+    <row r="13" spans="2:13" ht="50.25">
+      <c r="B13" s="87"/>
+      <c r="C13" s="88"/>
+      <c r="D13" s="89"/>
+      <c r="E13" s="77" t="s">
+        <v>189</v>
+      </c>
+      <c r="F13" s="78" t="s">
+        <v>190</v>
+      </c>
+      <c r="G13" s="77" t="s">
+        <v>191</v>
+      </c>
+      <c r="H13" s="78" t="s">
+        <v>192</v>
+      </c>
+      <c r="I13" s="77" t="s">
+        <v>193</v>
+      </c>
+      <c r="J13" s="78" t="s">
+        <v>194</v>
+      </c>
+      <c r="K13" s="77"/>
+      <c r="L13" s="78"/>
+    </row>
+    <row r="14" spans="2:13" ht="51">
+      <c r="B14" s="87"/>
+      <c r="C14" s="88"/>
+      <c r="D14" s="89"/>
+      <c r="E14" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="F14" s="80" t="s">
+        <v>196</v>
+      </c>
+      <c r="G14" s="79"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="J14" s="80" t="s">
+        <v>197</v>
+      </c>
+      <c r="K14" s="81"/>
+      <c r="L14" s="80"/>
+    </row>
+    <row r="15" spans="2:13" s="57" customFormat="1" ht="50.25">
+      <c r="B15" s="87"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="76"/>
+      <c r="E15" s="83" t="s">
+        <v>198</v>
+      </c>
+      <c r="F15" s="84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G15" s="83"/>
+      <c r="H15" s="84"/>
+      <c r="I15" s="83" t="s">
+        <v>200</v>
+      </c>
+      <c r="J15" s="84" t="s">
+        <v>201</v>
+      </c>
+      <c r="K15" s="83"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="56"/>
+    </row>
+    <row r="16" spans="2:13" s="57" customFormat="1" ht="51">
+      <c r="B16" s="87"/>
+      <c r="C16" s="91" t="s">
+        <v>202</v>
+      </c>
+      <c r="D16" s="92"/>
+      <c r="E16" s="72" t="s">
+        <v>184</v>
+      </c>
+      <c r="F16" s="73" t="s">
+        <v>203</v>
+      </c>
+      <c r="G16" s="72" t="s">
+        <v>186</v>
+      </c>
+      <c r="H16" s="73" t="s">
+        <v>204</v>
+      </c>
+      <c r="I16" s="72" t="s">
+        <v>184</v>
+      </c>
+      <c r="J16" s="73" t="s">
+        <v>205</v>
+      </c>
+      <c r="K16" s="72"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="56"/>
+    </row>
+    <row r="17" spans="2:15" s="57" customFormat="1" ht="50.25">
+      <c r="B17" s="87"/>
+      <c r="C17" s="93"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="77" t="s">
+        <v>189</v>
+      </c>
+      <c r="F17" s="78" t="s">
+        <v>190</v>
+      </c>
+      <c r="G17" s="77" t="s">
+        <v>191</v>
+      </c>
+      <c r="H17" s="78" t="s">
+        <v>192</v>
+      </c>
+      <c r="I17" s="77" t="s">
+        <v>189</v>
+      </c>
+      <c r="J17" s="78" t="s">
+        <v>206</v>
+      </c>
+      <c r="K17" s="77"/>
+      <c r="L17" s="78"/>
+      <c r="M17" s="56"/>
+    </row>
+    <row r="18" spans="2:15" s="57" customFormat="1" ht="51" customHeight="1">
+      <c r="B18" s="87"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="F18" s="80" t="s">
+        <v>207</v>
+      </c>
+      <c r="G18" s="79"/>
+      <c r="H18" s="80"/>
+      <c r="I18" s="79"/>
+      <c r="J18" s="80"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="80"/>
+      <c r="M18" s="56"/>
+    </row>
+    <row r="19" spans="2:15" s="57" customFormat="1" ht="50.25">
+      <c r="B19" s="87"/>
+      <c r="C19" s="94"/>
+      <c r="D19" s="92"/>
+      <c r="E19" s="83" t="s">
+        <v>208</v>
+      </c>
+      <c r="F19" s="84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G19" s="83"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="83"/>
+      <c r="J19" s="84"/>
+      <c r="K19" s="83"/>
+      <c r="L19" s="84"/>
+      <c r="M19" s="56"/>
+    </row>
+    <row r="20" spans="2:15" s="57" customFormat="1" ht="51" customHeight="1">
+      <c r="B20" s="87"/>
+      <c r="C20" s="86" t="s">
+        <v>209</v>
+      </c>
+      <c r="D20" s="71" t="s">
+        <v>210</v>
+      </c>
+      <c r="E20" s="72" t="s">
+        <v>184</v>
+      </c>
+      <c r="F20" s="73" t="s">
+        <v>211</v>
+      </c>
+      <c r="G20" s="72" t="s">
+        <v>186</v>
+      </c>
+      <c r="H20" s="73" t="s">
+        <v>212</v>
+      </c>
+      <c r="I20" s="72" t="s">
+        <v>195</v>
+      </c>
+      <c r="J20" s="73" t="s">
+        <v>213</v>
+      </c>
+      <c r="K20" s="72"/>
+      <c r="L20" s="73"/>
+      <c r="M20" s="56"/>
+    </row>
+    <row r="21" spans="2:15" ht="50.25">
+      <c r="B21" s="87"/>
+      <c r="C21" s="88"/>
+      <c r="D21" s="89"/>
+      <c r="E21" s="77" t="s">
+        <v>214</v>
+      </c>
+      <c r="F21" s="78" t="s">
+        <v>190</v>
+      </c>
+      <c r="G21" s="77" t="s">
+        <v>215</v>
+      </c>
+      <c r="H21" s="78" t="s">
+        <v>192</v>
+      </c>
+      <c r="I21" s="77" t="s">
+        <v>200</v>
+      </c>
+      <c r="J21" s="78" t="s">
+        <v>194</v>
+      </c>
+      <c r="K21" s="77"/>
+      <c r="L21" s="78"/>
+    </row>
+    <row r="22" spans="2:15" ht="51">
+      <c r="B22" s="87"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="89"/>
+      <c r="E22" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="F22" s="80" t="s">
+        <v>216</v>
+      </c>
+      <c r="G22" s="79"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="79" t="s">
+        <v>195</v>
+      </c>
+      <c r="J22" s="80" t="s">
+        <v>217</v>
+      </c>
+      <c r="K22" s="81"/>
+      <c r="L22" s="80"/>
+    </row>
+    <row r="23" spans="2:15" ht="50.25">
+      <c r="B23" s="96"/>
+      <c r="C23" s="90"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="83" t="s">
+        <v>198</v>
+      </c>
+      <c r="F23" s="84" t="s">
+        <v>199</v>
+      </c>
+      <c r="G23" s="83"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="83" t="s">
+        <v>198</v>
+      </c>
+      <c r="J23" s="84" t="s">
+        <v>199</v>
+      </c>
+      <c r="K23" s="83"/>
+      <c r="L23" s="84"/>
+    </row>
+    <row r="24" spans="2:15" ht="45.75" customHeight="1">
+      <c r="B24" s="97" t="s">
+        <v>218</v>
+      </c>
+      <c r="C24" s="98"/>
+      <c r="D24" s="71" t="s">
+        <v>219</v>
+      </c>
+      <c r="E24" s="72" t="s">
+        <v>220</v>
+      </c>
+      <c r="F24" s="73" t="s">
+        <v>221</v>
+      </c>
+      <c r="G24" s="72" t="s">
+        <v>222</v>
+      </c>
+      <c r="H24" s="73" t="s">
+        <v>223</v>
+      </c>
+      <c r="I24" s="72" t="s">
+        <v>224</v>
+      </c>
+      <c r="J24" s="73" t="s">
+        <v>225</v>
+      </c>
+      <c r="K24" s="72" t="s">
+        <v>226</v>
+      </c>
+      <c r="L24" s="73" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="25" spans="2:15" ht="50.25">
+      <c r="B25" s="99"/>
+      <c r="C25" s="100"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="77" t="s">
+        <v>228</v>
+      </c>
+      <c r="F25" s="78" t="s">
+        <v>229</v>
+      </c>
+      <c r="G25" s="77" t="s">
+        <v>230</v>
+      </c>
+      <c r="H25" s="78" t="s">
+        <v>231</v>
+      </c>
+      <c r="I25" s="77" t="s">
+        <v>232</v>
+      </c>
+      <c r="J25" s="78" t="s">
+        <v>233</v>
+      </c>
+      <c r="K25" s="77" t="s">
+        <v>234</v>
+      </c>
+      <c r="L25" s="78" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="26" spans="2:15" ht="45.75" customHeight="1">
+      <c r="B26" s="97" t="s">
+        <v>102</v>
+      </c>
+      <c r="C26" s="98"/>
+      <c r="D26" s="71" t="s">
+        <v>102</v>
+      </c>
+      <c r="E26" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="F26" s="80" t="s">
+        <v>237</v>
+      </c>
+      <c r="G26" s="79"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="79"/>
+      <c r="J26" s="80"/>
+      <c r="K26" s="81"/>
+      <c r="L26" s="80"/>
+    </row>
+    <row r="27" spans="2:15" s="56" customFormat="1" ht="50.25">
+      <c r="B27" s="101"/>
+      <c r="C27" s="102"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="83" t="s">
+        <v>238</v>
+      </c>
+      <c r="F27" s="84" t="s">
+        <v>239</v>
+      </c>
+      <c r="G27" s="83"/>
+      <c r="H27" s="84"/>
+      <c r="I27" s="83"/>
+      <c r="J27" s="84"/>
+      <c r="K27" s="83"/>
+      <c r="L27" s="84"/>
+      <c r="N27" s="57"/>
+      <c r="O27" s="57"/>
+    </row>
+    <row r="28" spans="2:15" ht="45.75" customHeight="1">
+      <c r="B28" s="101"/>
+      <c r="C28" s="102"/>
+      <c r="D28" s="71" t="s">
+        <v>219</v>
+      </c>
+      <c r="E28" s="72" t="s">
+        <v>240</v>
+      </c>
+      <c r="F28" s="73" t="s">
+        <v>241</v>
+      </c>
+      <c r="G28" s="72"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="72" t="s">
+        <v>240</v>
+      </c>
+      <c r="J28" s="73" t="s">
+        <v>242</v>
+      </c>
+      <c r="K28" s="72" t="s">
+        <v>243</v>
+      </c>
+      <c r="L28" s="73" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="29" spans="2:15" s="56" customFormat="1" ht="50.25">
+      <c r="B29" s="101"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="76"/>
+      <c r="E29" s="77" t="s">
+        <v>245</v>
+      </c>
+      <c r="F29" s="78" t="s">
+        <v>246</v>
+      </c>
+      <c r="G29" s="77"/>
+      <c r="H29" s="78"/>
+      <c r="I29" s="77" t="s">
+        <v>245</v>
+      </c>
+      <c r="J29" s="78" t="s">
+        <v>246</v>
+      </c>
+      <c r="K29" s="77" t="s">
+        <v>247</v>
+      </c>
+      <c r="L29" s="78" t="s">
+        <v>248</v>
+      </c>
+      <c r="N29" s="57"/>
+      <c r="O29" s="57"/>
+    </row>
+    <row r="30" spans="2:15" ht="45.75" customHeight="1">
+      <c r="B30" s="101"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="71" t="s">
+        <v>249</v>
+      </c>
+      <c r="E30" s="79"/>
+      <c r="F30" s="80"/>
+      <c r="G30" s="79"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="79"/>
+      <c r="J30" s="80"/>
+      <c r="K30" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="L30" s="80" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="31" spans="2:15" s="56" customFormat="1" ht="50.25">
+      <c r="B31" s="99"/>
+      <c r="C31" s="100"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="84"/>
+      <c r="G31" s="83"/>
+      <c r="H31" s="84"/>
+      <c r="I31" s="83"/>
+      <c r="J31" s="84"/>
+      <c r="K31" s="83" t="s">
+        <v>247</v>
+      </c>
+      <c r="L31" s="84" t="s">
+        <v>248</v>
+      </c>
+      <c r="N31" s="57"/>
+      <c r="O31" s="57"/>
+    </row>
+    <row r="32" spans="2:15" ht="45.75" customHeight="1">
+      <c r="B32" s="97" t="s">
+        <v>251</v>
+      </c>
+      <c r="C32" s="98"/>
+      <c r="D32" s="71" t="s">
+        <v>157</v>
+      </c>
+      <c r="E32" s="72"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="72" t="s">
+        <v>252</v>
+      </c>
+      <c r="L32" s="73" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" ht="50.25">
+      <c r="B33" s="99"/>
+      <c r="C33" s="100"/>
+      <c r="D33" s="76"/>
+      <c r="E33" s="77"/>
+      <c r="F33" s="78"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="78"/>
+      <c r="I33" s="77"/>
+      <c r="J33" s="78"/>
+      <c r="K33" s="77" t="s">
+        <v>254</v>
+      </c>
+      <c r="L33" s="78" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" ht="51">
+      <c r="B34" s="97" t="s">
+        <v>256</v>
+      </c>
+      <c r="C34" s="98"/>
+      <c r="D34" s="71" t="s">
+        <v>210</v>
+      </c>
+      <c r="E34" s="79"/>
+      <c r="F34" s="80"/>
+      <c r="G34" s="79"/>
+      <c r="H34" s="80"/>
+      <c r="I34" s="79"/>
+      <c r="J34" s="80"/>
+      <c r="K34" s="81" t="s">
+        <v>257</v>
+      </c>
+      <c r="L34" s="80" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" ht="50.25">
+      <c r="B35" s="99"/>
+      <c r="C35" s="100"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="83"/>
+      <c r="F35" s="84"/>
+      <c r="G35" s="83"/>
+      <c r="H35" s="84"/>
+      <c r="I35" s="83"/>
+      <c r="J35" s="84"/>
+      <c r="K35" s="83" t="s">
+        <v>193</v>
+      </c>
+      <c r="L35" s="84" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" s="57" customFormat="1">
+      <c r="B37" s="54"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="54"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
+      <c r="J37" s="55"/>
+      <c r="K37" s="55"/>
+      <c r="L37" s="55"/>
+      <c r="M37" s="56"/>
+    </row>
+    <row r="38" spans="2:13" s="57" customFormat="1">
+      <c r="B38" s="54"/>
+      <c r="C38" s="54"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="55"/>
+      <c r="J38" s="55"/>
+      <c r="K38" s="55"/>
+      <c r="L38" s="55"/>
+      <c r="M38" s="56"/>
+    </row>
+    <row r="39" spans="2:13" s="57" customFormat="1">
+      <c r="B39" s="54"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="55"/>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="55"/>
+      <c r="K39" s="55"/>
+      <c r="L39" s="55"/>
+      <c r="M39" s="56"/>
+    </row>
+    <row r="40" spans="2:13" s="57" customFormat="1">
+      <c r="B40" s="54"/>
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="55"/>
+      <c r="K40" s="55"/>
+      <c r="L40" s="55"/>
+      <c r="M40" s="56"/>
+    </row>
+    <row r="41" spans="2:13" s="57" customFormat="1">
+      <c r="B41" s="54"/>
+      <c r="C41" s="54"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="55"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="55"/>
+      <c r="J41" s="55"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="55"/>
+      <c r="M41" s="56"/>
+    </row>
+    <row r="42" spans="2:13" s="57" customFormat="1">
+      <c r="B42" s="54"/>
+      <c r="C42" s="54"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="55"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="55"/>
+      <c r="J42" s="55"/>
+      <c r="K42" s="55"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="56"/>
+    </row>
+    <row r="43" spans="2:13" s="57" customFormat="1">
+      <c r="B43" s="54"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="55"/>
+      <c r="K43" s="55"/>
+      <c r="L43" s="55"/>
+      <c r="M43" s="56"/>
+    </row>
+    <row r="44" spans="2:13" s="57" customFormat="1">
+      <c r="B44" s="54"/>
+      <c r="C44" s="54"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="55"/>
+      <c r="F44" s="55"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="55"/>
+      <c r="J44" s="55"/>
+      <c r="K44" s="55"/>
+      <c r="L44" s="55"/>
+      <c r="M44" s="56"/>
+    </row>
+    <row r="45" spans="2:13" s="57" customFormat="1">
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="55"/>
+      <c r="F45" s="55"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="55"/>
+      <c r="J45" s="55"/>
+      <c r="K45" s="55"/>
+      <c r="L45" s="55"/>
+      <c r="M45" s="56"/>
+    </row>
+    <row r="46" spans="2:13" s="57" customFormat="1">
+      <c r="B46" s="54"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="55"/>
+      <c r="F46" s="55"/>
+      <c r="G46" s="55"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="55"/>
+      <c r="J46" s="55"/>
+      <c r="K46" s="55"/>
+      <c r="L46" s="55"/>
+      <c r="M46" s="56"/>
+    </row>
+    <row r="47" spans="2:13" s="57" customFormat="1">
+      <c r="B47" s="54"/>
+      <c r="C47" s="54"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="55"/>
+      <c r="F47" s="55"/>
+      <c r="G47" s="55"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="55"/>
+      <c r="J47" s="55"/>
+      <c r="K47" s="55"/>
+      <c r="L47" s="55"/>
+      <c r="M47" s="56"/>
+    </row>
+    <row r="48" spans="2:13" s="57" customFormat="1">
+      <c r="B48" s="54"/>
+      <c r="C48" s="54"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="55"/>
+      <c r="F48" s="55"/>
+      <c r="G48" s="55"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="55"/>
+      <c r="J48" s="55"/>
+      <c r="K48" s="55"/>
+      <c r="L48" s="55"/>
+      <c r="M48" s="56"/>
+    </row>
+    <row r="49" spans="2:13" s="57" customFormat="1">
+      <c r="B49" s="54"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="55"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="55"/>
+      <c r="J49" s="55"/>
+      <c r="K49" s="55"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="56"/>
+    </row>
+    <row r="50" spans="2:13" s="57" customFormat="1">
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="55"/>
+      <c r="F50" s="55"/>
+      <c r="G50" s="55"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="55"/>
+      <c r="J50" s="55"/>
+      <c r="K50" s="55"/>
+      <c r="L50" s="55"/>
+      <c r="M50" s="56"/>
+    </row>
+    <row r="51" spans="2:13" s="57" customFormat="1">
+      <c r="B51" s="54"/>
+      <c r="C51" s="54"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="55"/>
+      <c r="F51" s="55"/>
+      <c r="G51" s="55"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="55"/>
+      <c r="J51" s="55"/>
+      <c r="K51" s="55"/>
+      <c r="L51" s="55"/>
+      <c r="M51" s="56"/>
+    </row>
+    <row r="52" spans="2:13" s="57" customFormat="1">
+      <c r="B52" s="54"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="55"/>
+      <c r="F52" s="55"/>
+      <c r="G52" s="55"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="55"/>
+      <c r="J52" s="55"/>
+      <c r="K52" s="55"/>
+      <c r="L52" s="55"/>
+      <c r="M52" s="56"/>
+    </row>
+    <row r="53" spans="2:13" s="57" customFormat="1">
+      <c r="B53" s="54"/>
+      <c r="C53" s="54"/>
+      <c r="D53" s="54"/>
+      <c r="E53" s="55"/>
+      <c r="F53" s="55"/>
+      <c r="G53" s="55"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="55"/>
+      <c r="J53" s="55"/>
+      <c r="K53" s="55"/>
+      <c r="L53" s="55"/>
+      <c r="M53" s="56"/>
+    </row>
+    <row r="54" spans="2:13" s="57" customFormat="1">
+      <c r="B54" s="54"/>
+      <c r="C54" s="54"/>
+      <c r="D54" s="54"/>
+      <c r="E54" s="55"/>
+      <c r="F54" s="55"/>
+      <c r="G54" s="55"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="55"/>
+      <c r="J54" s="55"/>
+      <c r="K54" s="55"/>
+      <c r="L54" s="55"/>
+      <c r="M54" s="56"/>
+    </row>
+    <row r="55" spans="2:13" s="57" customFormat="1">
+      <c r="B55" s="54"/>
+      <c r="C55" s="54"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="55"/>
+      <c r="F55" s="55"/>
+      <c r="G55" s="55"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="55"/>
+      <c r="J55" s="55"/>
+      <c r="K55" s="55"/>
+      <c r="L55" s="55"/>
+      <c r="M55" s="56"/>
+    </row>
+    <row r="56" spans="2:13" s="57" customFormat="1">
+      <c r="B56" s="54"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="55"/>
+      <c r="F56" s="55"/>
+      <c r="G56" s="55"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="55"/>
+      <c r="J56" s="55"/>
+      <c r="K56" s="55"/>
+      <c r="L56" s="55"/>
+      <c r="M56" s="56"/>
+    </row>
+    <row r="57" spans="2:13" s="57" customFormat="1">
+      <c r="B57" s="54"/>
+      <c r="C57" s="54"/>
+      <c r="D57" s="54"/>
+      <c r="E57" s="55"/>
+      <c r="F57" s="55"/>
+      <c r="G57" s="55"/>
+      <c r="H57" s="55"/>
+      <c r="I57" s="55"/>
+      <c r="J57" s="55"/>
+      <c r="K57" s="55"/>
+      <c r="L57" s="55"/>
+      <c r="M57" s="56"/>
+    </row>
+    <row r="58" spans="2:13" s="57" customFormat="1">
+      <c r="B58" s="54"/>
+      <c r="C58" s="54"/>
+      <c r="D58" s="54"/>
+      <c r="E58" s="55"/>
+      <c r="F58" s="55"/>
+      <c r="G58" s="55"/>
+      <c r="H58" s="55"/>
+      <c r="I58" s="55"/>
+      <c r="J58" s="55"/>
+      <c r="K58" s="55"/>
+      <c r="L58" s="55"/>
+      <c r="M58" s="56"/>
+    </row>
+  </sheetData>
+  <mergeCells count="33">
+    <mergeCell ref="B32:C33"/>
+    <mergeCell ref="D32:D33"/>
+    <mergeCell ref="B34:C35"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="B24:C25"/>
+    <mergeCell ref="D24:D25"/>
+    <mergeCell ref="B26:C31"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="B12:B23"/>
+    <mergeCell ref="C12:C15"/>
+    <mergeCell ref="D12:D15"/>
+    <mergeCell ref="C16:C19"/>
+    <mergeCell ref="C20:C23"/>
+    <mergeCell ref="D20:D23"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:L2"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+  </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>